--- a/runs/RELX/2026-10-14/bear/scratch/b_bbb/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/b_bbb/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2042.187203326114</v>
+        <v>2100.047103566721</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.103145</v>
+        <v>0.0953618</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.09633615530800001</v>
+        <v>0.089550605884</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11125.7140372812</v>
+        <v>11294.45458831833</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>37718.31987944588</v>
+        <v>41398.22346158132</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>24934.77906219554</v>
+        <v>28142.86938387483</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>36060.49309947673</v>
+        <v>39437.32397219317</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>29063.49309947673</v>
+        <v>32440.32397219317</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>28114.03153537082</v>
+        <v>31567.02321910576</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>16.12269839333363</v>
+        <v>18.10290330992505</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1612.269839333363</v>
+        <v>1810.290330992505</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.418163176</v>
+        <v>-0.3467014323</v>
       </c>
     </row>
   </sheetData>
